--- a/feedback_forms/013_winning_move_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/013_winning_move_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'clarity'}</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Clarity'}</t>
+          <t>Clarity</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'timeliness'}</t>
+          <t>timeliness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Timeliness'}</t>
+          <t>Timeliness</t>
         </is>
       </c>
     </row>
